--- a/registration_forms/033_healthy_snacking_expo_registration--registration_forms.xlsx
+++ b/registration_forms/033_healthy_snacking_expo_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'vegan'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Vegan'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'vegetarian'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Vegetarian'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'omnivore'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Omnivore'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'gluten-free'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Gluten-free'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'none'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'None'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'nutrition'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Nutrition'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'cooking'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Cooking'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'wellness'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Wellness'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'product'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Product'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'breakfast'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Breakfast'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'lunch'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Lunch'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'dinner'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Dinner'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'snack'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Snack'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'morning'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Morning'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'afternoon'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Afternoon'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'evening'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'Evening'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'8:00_am_-_9:00_am'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': '8:00 AM - 9:00 AM'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'9:00_am_-_10:00_am'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': '9:00 AM - 10:00 AM'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'10:00_am_-_11:00_am'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': '10:00 AM - 11:00 AM'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'11:00_am_-_12:00_pm'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': '11:00 AM - 12:00 PM'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'12:00_pm_-_1:00_pm'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': '12:00 PM - 1:00 PM'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_'1:00_pm_-_2:00_pm'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': '1:00 PM - 2:00 PM'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'2:00_pm_-_3:00_pm'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': '2:00 PM - 3:00 PM'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'3:00_pm_-_4:00_pm'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': '3:00 PM - 4:00 PM'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'4:00_pm_-_5:00_pm'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': '4:00 PM - 5:00 PM'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'5:00_pm_-_6:00_pm'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': '5:00 PM - 6:00 PM'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'6:00_pm_-_7:00_pm'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': '6:00 PM - 7:00 PM'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'7:00_pm_-_8:00_pm'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': '7:00 PM - 8:00 PM'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_'8:00_pm_-_9:00_pm'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': '8:00 PM - 9:00 PM'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
